--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ33"/>
+  <dimension ref="A1:AZ64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1544,10 +1544,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>389140</v>
+        <v>136990661</v>
       </c>
       <c r="B9" t="n">
-        <v>91909</v>
+        <v>92109</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,34 +1555,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Båtsviksberget, 430 m SSV om, Vb</t>
+          <t>Gröthällan, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759507</v>
+        <v>759582</v>
       </c>
       <c r="R9" t="n">
-        <v>7074272</v>
+        <v>7074092</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1609,12 +1609,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2011-06-05</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2011-06-05</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1625,41 +1635,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Äldre granskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Gudrun Norstedt</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Gudrun Norstedt</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/389140</t>
+          <t>https://artportalen.se/Sighting/136990661</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>389141</v>
+        <v>136990666</v>
       </c>
       <c r="B10" t="n">
-        <v>91909</v>
+        <v>92109</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,34 +1667,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Båtsviksberget, 430 m SSV om, Vb</t>
+          <t>Gröthällan, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759505</v>
+        <v>759632</v>
       </c>
       <c r="R10" t="n">
-        <v>7074277</v>
+        <v>7074144</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1721,17 +1721,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2011-06-05</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2011-06-05</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På samma låga som stjärntagging</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1742,41 +1747,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Äldre granskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Gudrun Norstedt</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Gudrun Norstedt</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/389141</t>
+          <t>https://artportalen.se/Sighting/136990666</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130261227</v>
+        <v>136990671</v>
       </c>
       <c r="B11" t="n">
-        <v>91909</v>
+        <v>92109</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1784,34 +1779,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>NV Gröthällberget, Vb</t>
+          <t>Gröthällan, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759410</v>
+        <v>759523</v>
       </c>
       <c r="R11" t="n">
-        <v>7074242</v>
+        <v>7074171</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1838,12 +1833,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1854,86 +1859,66 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>Granlåga rotknäckt</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga rotknäckt</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261227</t>
+          <t>https://artportalen.se/Sighting/136990671</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130261232</v>
+        <v>136990685</v>
       </c>
       <c r="B12" t="n">
-        <v>92632</v>
+        <v>92109</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>NV Gröthällberget, Vb</t>
+          <t>Gröthällan, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759330</v>
+        <v>759462</v>
       </c>
       <c r="R12" t="n">
-        <v>7074184</v>
+        <v>7074312</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1960,12 +1945,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1976,73 +1971,53 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>Stående död</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående död</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261232</t>
+          <t>https://artportalen.se/Sighting/136990685</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1586002</v>
+        <v>389140</v>
       </c>
       <c r="B13" t="n">
-        <v>91872</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2052,10 +2027,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759505</v>
+        <v>759507</v>
       </c>
       <c r="R13" t="n">
-        <v>7074277</v>
+        <v>7074272</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2123,54 +2098,54 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1586002</t>
+          <t>https://artportalen.se/Sighting/389140</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122748168</v>
+        <v>389141</v>
       </c>
       <c r="B14" t="n">
-        <v>91872</v>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Jenberget NÖ, Vb</t>
+          <t>Båtsviksberget, 430 m SSV om, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759334</v>
+        <v>759505</v>
       </c>
       <c r="R14" t="n">
-        <v>7074199</v>
+        <v>7074277</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2194,12 +2169,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2011-06-05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2011-06-05</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På samma låga som stjärntagging</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2210,57 +2190,63 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Äldre granskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Gudrun Norstedt</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jessica  Åström</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Gudrun Norstedt</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122748168</t>
+          <t>https://artportalen.se/Sighting/389141</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130261223</v>
+        <v>130261227</v>
       </c>
       <c r="B15" t="n">
-        <v>91872</v>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2270,10 +2256,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>759450</v>
+        <v>759410</v>
       </c>
       <c r="R15" t="n">
-        <v>7074279</v>
+        <v>7074242</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2329,12 +2315,12 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>Granlåga knäckt</t>
+          <t>Granlåga rotknäckt</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga knäckt</t>
+          <t>Picea abies # Granlåga rotknäckt</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2351,16 +2337,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261223</t>
+          <t>https://artportalen.se/Sighting/130261227</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130261224</v>
+        <v>136990687</v>
       </c>
       <c r="B16" t="n">
-        <v>91872</v>
+        <v>92124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,34 +2354,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>1205</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>NV Gröthällberget, Vb</t>
+          <t>Gröthällan, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759568</v>
+        <v>759463</v>
       </c>
       <c r="R16" t="n">
-        <v>7074103</v>
+        <v>7074370</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2422,12 +2408,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2438,51 +2434,31 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>Äldre granlåga</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre granlåga</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261224</t>
+          <t>https://artportalen.se/Sighting/136990687</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130261225</v>
+        <v>136990689</v>
       </c>
       <c r="B17" t="n">
-        <v>91872</v>
+        <v>92124</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2490,34 +2466,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>1205</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>NV Gröthällberget, Vb</t>
+          <t>Gröthällan, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759453</v>
+        <v>759505</v>
       </c>
       <c r="R17" t="n">
-        <v>7074313</v>
+        <v>7074278</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2544,12 +2520,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2560,51 +2546,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>Tunnare granlåga invid äldre talltorraka</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies # Tunnare granlåga invid äldre talltorraka</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261225</t>
+          <t>https://artportalen.se/Sighting/136990689</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130261226</v>
+        <v>136990656</v>
       </c>
       <c r="B18" t="n">
-        <v>91872</v>
+        <v>96568</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2612,34 +2578,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>NV Gröthällberget, Vb</t>
+          <t>Gröthällan, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759410</v>
+        <v>759491</v>
       </c>
       <c r="R18" t="n">
-        <v>7074242</v>
+        <v>7074127</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2666,12 +2632,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2682,92 +2658,69 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>Granlåga rotknäckt</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga rotknäckt</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261226</t>
+          <t>https://artportalen.se/Sighting/136990656</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>114558886</v>
+        <v>136990694</v>
       </c>
       <c r="B19" t="n">
-        <v>79327</v>
+        <v>96568</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>300m NO Gröthällberget, Vb</t>
+          <t>Gröthällan, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759614</v>
+        <v>759400</v>
       </c>
       <c r="R19" t="n">
-        <v>7074148</v>
+        <v>7074156</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2791,12 +2744,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2805,34 +2768,33 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Andreas Drott</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Andreas Drott, Karl-Henrik  Drott</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114558886</t>
+          <t>https://artportalen.se/Sighting/136990694</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130261235</v>
+        <v>136990655</v>
       </c>
       <c r="B20" t="n">
-        <v>57950</v>
+        <v>96565</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2840,39 +2802,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>2812</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>NV Gröthällberget, Vb</t>
+          <t>Gröthällan, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759616</v>
+        <v>759488</v>
       </c>
       <c r="R20" t="n">
-        <v>7074094</v>
+        <v>7074200</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2899,12 +2856,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2915,51 +2882,31 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>Granhögstubbe knäckt</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe knäckt</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261235</t>
+          <t>https://artportalen.se/Sighting/136990655</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130261236</v>
+        <v>136990691</v>
       </c>
       <c r="B21" t="n">
-        <v>57950</v>
+        <v>96565</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2967,39 +2914,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>2812</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>NV Gröthällberget, Vb</t>
+          <t>Gröthällan, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759588</v>
+        <v>759513</v>
       </c>
       <c r="R21" t="n">
-        <v>7074157</v>
+        <v>7074245</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3026,12 +2968,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3042,51 +2994,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>Granhögstubbe grov, knäckt</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe grov, knäckt</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261236</t>
+          <t>https://artportalen.se/Sighting/136990691</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130261237</v>
+        <v>130261232</v>
       </c>
       <c r="B22" t="n">
-        <v>57950</v>
+        <v>92632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3094,39 +3026,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759528</v>
+        <v>759330</v>
       </c>
       <c r="R22" t="n">
-        <v>7074150</v>
+        <v>7074184</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3161,11 +3088,6 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Högt upp</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3187,12 +3109,12 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Stående död</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Stående död</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3209,16 +3131,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261237</t>
+          <t>https://artportalen.se/Sighting/130261232</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130261238</v>
+        <v>1586002</v>
       </c>
       <c r="B23" t="n">
-        <v>57950</v>
+        <v>91872</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3226,39 +3148,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>NV Gröthällberget, Vb</t>
+          <t>Båtsviksberget, 430 m SSV om, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>759413</v>
+        <v>759505</v>
       </c>
       <c r="R23" t="n">
-        <v>7074262</v>
+        <v>7074277</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3285,17 +3202,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2011-06-05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Vid basen</t>
+          <t>2011-06-05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3307,50 +3219,40 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies # Levande</t>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Äldre granskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Gudrun Norstedt</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Gudrun Norstedt</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261238</t>
+          <t>https://artportalen.se/Sighting/1586002</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130261239</v>
+        <v>122748168</v>
       </c>
       <c r="B24" t="n">
-        <v>57950</v>
+        <v>91872</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3358,42 +3260,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>NV Gröthällberget, Vb</t>
+          <t>Jenberget NÖ, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759521</v>
+        <v>759334</v>
       </c>
       <c r="R24" t="n">
-        <v>7074165</v>
+        <v>7074199</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3417,12 +3314,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3433,51 +3330,35 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies # Levande</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Jessica  Åström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261239</t>
+          <t>https://artportalen.se/Sighting/122748168</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130261240</v>
+        <v>130261223</v>
       </c>
       <c r="B25" t="n">
-        <v>57950</v>
+        <v>91872</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3485,39 +3366,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759411</v>
+        <v>759450</v>
       </c>
       <c r="R25" t="n">
-        <v>7074135</v>
+        <v>7074279</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3573,12 +3449,12 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Granlåga knäckt</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Granlåga knäckt</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3595,16 +3471,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261240</t>
+          <t>https://artportalen.se/Sighting/130261223</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130261241</v>
+        <v>130261224</v>
       </c>
       <c r="B26" t="n">
-        <v>57950</v>
+        <v>91872</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3612,39 +3488,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759358</v>
+        <v>759568</v>
       </c>
       <c r="R26" t="n">
-        <v>7074193</v>
+        <v>7074103</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3700,12 +3571,12 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>Granlåga, knäckt</t>
+          <t>Äldre granlåga</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt</t>
+          <t>Picea abies # Äldre granlåga</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3722,16 +3593,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261241</t>
+          <t>https://artportalen.se/Sighting/130261224</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130261242</v>
+        <v>130261225</v>
       </c>
       <c r="B27" t="n">
-        <v>57950</v>
+        <v>91872</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3739,39 +3610,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>759521</v>
+        <v>759453</v>
       </c>
       <c r="R27" t="n">
-        <v>7074133</v>
+        <v>7074313</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3806,11 +3672,6 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Vid basen</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3832,12 +3693,12 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>Knäckt gran</t>
+          <t>Tunnare granlåga invid äldre talltorraka</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies # Knäckt gran</t>
+          <t>Picea abies # Tunnare granlåga invid äldre talltorraka</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3854,16 +3715,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261242</t>
+          <t>https://artportalen.se/Sighting/130261225</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130261243</v>
+        <v>130261226</v>
       </c>
       <c r="B28" t="n">
-        <v>57950</v>
+        <v>91872</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3871,39 +3732,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>759457</v>
+        <v>759410</v>
       </c>
       <c r="R28" t="n">
-        <v>7074149</v>
+        <v>7074242</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3938,11 +3794,6 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Kåda</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3962,9 +3813,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>Granlåga rotknäckt</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga rotknäckt</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3981,59 +3837,51 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261243</t>
+          <t>https://artportalen.se/Sighting/130261226</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130261228</v>
+        <v>136990652</v>
       </c>
       <c r="B29" t="n">
-        <v>57953</v>
+        <v>92076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>NV Gröthällberget, Vb</t>
+          <t>Gröthällan, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759417</v>
+        <v>759401</v>
       </c>
       <c r="R29" t="n">
-        <v>7074118</v>
+        <v>7074284</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4060,17 +3908,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4081,91 +3934,66 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL29" t="inlineStr">
-        <is>
-          <t>Stående död</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående död</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261228</t>
+          <t>https://artportalen.se/Sighting/136990652</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130261231</v>
+        <v>136990658</v>
       </c>
       <c r="B30" t="n">
-        <v>57953</v>
+        <v>92076</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>NV Gröthällberget, Vb</t>
+          <t>Gröthällan, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>759348</v>
+        <v>759565</v>
       </c>
       <c r="R30" t="n">
-        <v>7074185</v>
+        <v>7074114</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4192,17 +4020,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på granlåga</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4213,51 +4046,31 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL30" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261231</t>
+          <t>https://artportalen.se/Sighting/136990658</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130261249</v>
+        <v>136990669</v>
       </c>
       <c r="B31" t="n">
-        <v>58327</v>
+        <v>92076</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4265,42 +4078,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103015</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>NV Gröthällberget, Vb</t>
+          <t>Gröthällan, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>759466</v>
+        <v>759555</v>
       </c>
       <c r="R31" t="n">
-        <v>7074152</v>
+        <v>7074182</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4327,22 +4132,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4357,70 +4162,62 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261249</t>
+          <t>https://artportalen.se/Sighting/136990669</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130261233</v>
+        <v>136990683</v>
       </c>
       <c r="B32" t="n">
-        <v>58114</v>
+        <v>92076</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>NV Gröthällberget, Vb</t>
+          <t>Gröthällan, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>759425</v>
+        <v>759438</v>
       </c>
       <c r="R32" t="n">
-        <v>7074122</v>
+        <v>7074263</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4447,22 +4244,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4477,74 +4274,62 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261233</t>
+          <t>https://artportalen.se/Sighting/136990683</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130261234</v>
+        <v>136990684</v>
       </c>
       <c r="B33" t="n">
-        <v>58114</v>
+        <v>92076</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>NV Gröthällberget, Vb</t>
+          <t>Gröthällan, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>759386</v>
+        <v>759449</v>
       </c>
       <c r="R33" t="n">
-        <v>7074195</v>
+        <v>7074321</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4571,22 +4356,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4601,18 +4386,3718 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136990684</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>114558886</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>300m NO Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>759614</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7074148</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-02-03</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-02-03</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Andreas Drott</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Andreas Drott, Karl-Henrik  Drott</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114558886</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>136990648</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Gröthällan, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>759357</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7074202</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136990648</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>136990653</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Gröthällan, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>759430</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7074290</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136990653</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>136990657</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Gröthällan, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>759532</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7074133</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136990657</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>136990664</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Gröthällan, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>759609</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7074093</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136990664</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>136990665</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Gröthällan, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>759610</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7074115</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136990665</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>136990667</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Gröthällan, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>759580</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7074138</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136990667</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>136990679</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Gröthällan, Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>759412</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7074157</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136990679</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>136990680</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Gröthällan, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>759435</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7074157</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136990680</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>136990686</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Gröthällan, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>759454</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7074302</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136990686</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>136990688</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Gröthällan, Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>759542</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7074337</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136990688</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>136990690</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Gröthällan, Vb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>759513</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7074242</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136990690</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>136990692</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Gröthällan, Vb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>759539</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7074223</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136990692</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>130261235</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>759616</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7074094</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>Granhögstubbe knäckt</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe knäckt</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261235</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>130261236</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>759588</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7074157</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>Granhögstubbe grov, knäckt</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe grov, knäckt</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261236</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>130261237</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>759528</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7074150</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Högt upp</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL49" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies # Levande</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261237</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>130261238</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>759413</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7074262</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Vid basen</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL50" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Picea abies # Levande</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261238</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>130261239</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>759521</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7074165</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Picea abies # Levande</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261239</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>130261240</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>759411</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7074135</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL52" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Picea abies # Levande</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261240</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>130261241</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>759358</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7074193</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>Granlåga, knäckt</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga, knäckt</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261241</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>130261242</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>759521</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7074133</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Vid basen</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL54" t="inlineStr">
+        <is>
+          <t>Knäckt gran</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Picea abies # Knäckt gran</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261242</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>130261243</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>759457</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7074149</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Kåda</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261243</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>136990659</v>
+      </c>
+      <c r="B56" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Gröthällan, Vb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>759558</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7074114</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136990659</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>130261228</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>759417</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7074118</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>Stående död</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261228</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>130261231</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>759348</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7074185</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack på granlåga</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL58" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261231</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>136990670</v>
+      </c>
+      <c r="B59" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Gröthällan, Vb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>759545</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7074163</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Gammalt ringhack</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136990670</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>130261249</v>
+      </c>
+      <c r="B60" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>759466</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7074152</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261249</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>130261233</v>
+      </c>
+      <c r="B61" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>759425</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7074122</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261233</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>130261234</v>
+      </c>
+      <c r="B62" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>759386</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7074195</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/130261234</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>136990660</v>
+      </c>
+      <c r="B63" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Gröthällan, Vb</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>759548</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7074112</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136990660</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>136990668</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Gröthällan, Vb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>759580</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7074146</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136990668</t>
         </is>
       </c>
     </row>
@@ -4650,6 +8135,37 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ64"/>
+  <dimension ref="A1:AZ75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -807,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130261254</v>
+        <v>137016886</v>
       </c>
       <c r="B3" t="n">
-        <v>91905</v>
+        <v>92063</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,34 +818,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>NV Gröthällberget, Vb</t>
+          <t>Gröthällan, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759629</v>
+        <v>759457</v>
       </c>
       <c r="R3" t="n">
-        <v>7074125</v>
+        <v>7074159</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,17 +872,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre fruktkroppar</t>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,51 +898,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Stående död</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående död</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261254</t>
+          <t>https://artportalen.se/Sighting/137016886</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130261255</v>
+        <v>137016887</v>
       </c>
       <c r="B4" t="n">
-        <v>91905</v>
+        <v>92063</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,34 +930,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>112</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>NV Gröthällberget, Vb</t>
+          <t>Gröthällan, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759576</v>
+        <v>759491</v>
       </c>
       <c r="R4" t="n">
-        <v>7074103</v>
+        <v>7074170</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -999,12 +984,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,48 +1010,28 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Granstubbe knäckt</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies # Granstubbe knäckt</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261255</t>
+          <t>https://artportalen.se/Sighting/137016887</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130261256</v>
+        <v>130261254</v>
       </c>
       <c r="B5" t="n">
         <v>91905</v>
@@ -1091,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>759454</v>
+        <v>759629</v>
       </c>
       <c r="R5" t="n">
-        <v>7074134</v>
+        <v>7074125</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1129,6 +1104,11 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1150,12 +1130,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Granstubbe knäckt</t>
+          <t>Stående död</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe knäckt</t>
+          <t>Picea abies # Stående död</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1172,13 +1152,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261256</t>
+          <t>https://artportalen.se/Sighting/130261254</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130261257</v>
+        <v>130261255</v>
       </c>
       <c r="B6" t="n">
         <v>91905</v>
@@ -1213,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>759449</v>
+        <v>759576</v>
       </c>
       <c r="R6" t="n">
-        <v>7074314</v>
+        <v>7074103</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1272,12 +1252,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Stående död</t>
+          <t>Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död</t>
+          <t>Picea abies # Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1294,13 +1274,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261257</t>
+          <t>https://artportalen.se/Sighting/130261255</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130261258</v>
+        <v>130261256</v>
       </c>
       <c r="B7" t="n">
         <v>91905</v>
@@ -1335,10 +1315,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>759498</v>
+        <v>759454</v>
       </c>
       <c r="R7" t="n">
-        <v>7074364</v>
+        <v>7074134</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1394,12 +1374,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Stående död</t>
+          <t>Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död</t>
+          <t>Picea abies # Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1416,13 +1396,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261258</t>
+          <t>https://artportalen.se/Sighting/130261256</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130261259</v>
+        <v>130261257</v>
       </c>
       <c r="B8" t="n">
         <v>91905</v>
@@ -1457,10 +1437,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>759622</v>
+        <v>759449</v>
       </c>
       <c r="R8" t="n">
-        <v>7074145</v>
+        <v>7074314</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1538,16 +1518,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261259</t>
+          <t>https://artportalen.se/Sighting/130261257</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136990661</v>
+        <v>130261258</v>
       </c>
       <c r="B9" t="n">
-        <v>92109</v>
+        <v>91905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,14 +1555,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gröthällan, Vb</t>
+          <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759582</v>
+        <v>759498</v>
       </c>
       <c r="R9" t="n">
-        <v>7074092</v>
+        <v>7074364</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1609,22 +1589,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:56</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:56</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1635,31 +1605,51 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Stående död</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136990661</t>
+          <t>https://artportalen.se/Sighting/130261258</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136990666</v>
+        <v>130261259</v>
       </c>
       <c r="B10" t="n">
-        <v>92109</v>
+        <v>91905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1687,14 +1677,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gröthällan, Vb</t>
+          <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759632</v>
+        <v>759622</v>
       </c>
       <c r="R10" t="n">
-        <v>7074144</v>
+        <v>7074145</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1721,22 +1711,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1747,28 +1727,48 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Stående död</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136990666</t>
+          <t>https://artportalen.se/Sighting/130261259</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136990671</v>
+        <v>136990661</v>
       </c>
       <c r="B11" t="n">
         <v>92109</v>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759523</v>
+        <v>759582</v>
       </c>
       <c r="R11" t="n">
-        <v>7074171</v>
+        <v>7074092</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1874,13 +1874,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136990671</t>
+          <t>https://artportalen.se/Sighting/136990661</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136990685</v>
+        <v>136990666</v>
       </c>
       <c r="B12" t="n">
         <v>92109</v>
@@ -1915,10 +1915,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759462</v>
+        <v>759632</v>
       </c>
       <c r="R12" t="n">
-        <v>7074312</v>
+        <v>7074144</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1945,22 +1945,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1986,16 +1986,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136990685</t>
+          <t>https://artportalen.se/Sighting/136990666</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>389140</v>
+        <v>136990671</v>
       </c>
       <c r="B13" t="n">
-        <v>91909</v>
+        <v>92109</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2003,34 +2003,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Båtsviksberget, 430 m SSV om, Vb</t>
+          <t>Gröthällan, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759507</v>
+        <v>759523</v>
       </c>
       <c r="R13" t="n">
-        <v>7074272</v>
+        <v>7074171</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2057,12 +2057,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2011-06-05</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2011-06-05</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2073,41 +2083,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Äldre granskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Gudrun Norstedt</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Gudrun Norstedt</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/389140</t>
+          <t>https://artportalen.se/Sighting/136990671</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>389141</v>
+        <v>136990685</v>
       </c>
       <c r="B14" t="n">
-        <v>91909</v>
+        <v>92109</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2115,34 +2115,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Båtsviksberget, 430 m SSV om, Vb</t>
+          <t>Gröthällan, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759505</v>
+        <v>759462</v>
       </c>
       <c r="R14" t="n">
-        <v>7074277</v>
+        <v>7074312</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2169,17 +2169,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2011-06-05</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2011-06-05</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På samma låga som stjärntagging</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2190,41 +2195,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Äldre granskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Gudrun Norstedt</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Gudrun Norstedt</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/389141</t>
+          <t>https://artportalen.se/Sighting/136990685</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130261227</v>
+        <v>137017880</v>
       </c>
       <c r="B15" t="n">
-        <v>91909</v>
+        <v>92109</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2232,34 +2227,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>NV Gröthällberget, Vb</t>
+          <t>Gröthällan, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>759410</v>
+        <v>759438</v>
       </c>
       <c r="R15" t="n">
-        <v>7074242</v>
+        <v>7074273</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2286,12 +2281,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2302,73 +2307,53 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>Granlåga rotknäckt</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga rotknäckt</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Alva Danielsson, Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261227</t>
+          <t>https://artportalen.se/Sighting/137017880</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136990687</v>
+        <v>137017886</v>
       </c>
       <c r="B16" t="n">
-        <v>92124</v>
+        <v>92109</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1205</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2378,10 +2363,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759463</v>
+        <v>759553</v>
       </c>
       <c r="R16" t="n">
-        <v>7074370</v>
+        <v>7074152</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2408,22 +2393,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2438,62 +2423,62 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Alva Danielsson, Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136990687</t>
+          <t>https://artportalen.se/Sighting/137017886</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136990689</v>
+        <v>389140</v>
       </c>
       <c r="B17" t="n">
-        <v>92124</v>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gröthällan, Vb</t>
+          <t>Båtsviksberget, 430 m SSV om, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759505</v>
+        <v>759507</v>
       </c>
       <c r="R17" t="n">
-        <v>7074278</v>
+        <v>7074272</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2520,22 +2505,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:11</t>
+          <t>2011-06-05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:11</t>
+          <t>2011-06-05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2546,66 +2521,76 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Äldre granskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Gudrun Norstedt</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Gudrun Norstedt</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136990689</t>
+          <t>https://artportalen.se/Sighting/389140</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136990656</v>
+        <v>389141</v>
       </c>
       <c r="B18" t="n">
-        <v>96568</v>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gröthällan, Vb</t>
+          <t>Båtsviksberget, 430 m SSV om, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759491</v>
+        <v>759505</v>
       </c>
       <c r="R18" t="n">
-        <v>7074127</v>
+        <v>7074277</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2632,22 +2617,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:33</t>
+          <t>2011-06-05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:33</t>
+          <t>2011-06-05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På samma låga som stjärntagging</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2658,66 +2638,76 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Äldre granskog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Gudrun Norstedt</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Gudrun Norstedt</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136990656</t>
+          <t>https://artportalen.se/Sighting/389141</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136990694</v>
+        <v>130261227</v>
       </c>
       <c r="B19" t="n">
-        <v>96568</v>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gröthällan, Vb</t>
+          <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759400</v>
+        <v>759410</v>
       </c>
       <c r="R19" t="n">
-        <v>7074156</v>
+        <v>7074242</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2744,22 +2734,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2770,31 +2750,51 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Granlåga rotknäckt</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga rotknäckt</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136990694</t>
+          <t>https://artportalen.se/Sighting/130261227</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136990655</v>
+        <v>136990687</v>
       </c>
       <c r="B20" t="n">
-        <v>96565</v>
+        <v>92124</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2802,21 +2802,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2812</v>
+        <v>1205</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759488</v>
+        <v>759463</v>
       </c>
       <c r="R20" t="n">
-        <v>7074200</v>
+        <v>7074370</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2856,22 +2856,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2897,16 +2897,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136990655</t>
+          <t>https://artportalen.se/Sighting/136990687</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136990691</v>
+        <v>136990689</v>
       </c>
       <c r="B21" t="n">
-        <v>96565</v>
+        <v>92124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2914,21 +2914,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2812</v>
+        <v>1205</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2938,10 +2938,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759513</v>
+        <v>759505</v>
       </c>
       <c r="R21" t="n">
-        <v>7074245</v>
+        <v>7074278</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3009,16 +3009,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136990691</t>
+          <t>https://artportalen.se/Sighting/136990689</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130261232</v>
+        <v>136990656</v>
       </c>
       <c r="B22" t="n">
-        <v>92632</v>
+        <v>96568</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3026,34 +3026,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3298</v>
+        <v>2809</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>NV Gröthällberget, Vb</t>
+          <t>Gröthällan, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759330</v>
+        <v>759491</v>
       </c>
       <c r="R22" t="n">
-        <v>7074184</v>
+        <v>7074127</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3080,12 +3080,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3096,51 +3106,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>Stående död</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående död</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261232</t>
+          <t>https://artportalen.se/Sighting/136990656</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1586002</v>
+        <v>136990694</v>
       </c>
       <c r="B23" t="n">
-        <v>91872</v>
+        <v>96568</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3148,34 +3138,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Båtsviksberget, 430 m SSV om, Vb</t>
+          <t>Gröthällan, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>759505</v>
+        <v>759400</v>
       </c>
       <c r="R23" t="n">
-        <v>7074277</v>
+        <v>7074156</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3202,12 +3192,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2011-06-05</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2011-06-05</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3218,41 +3218,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Äldre granskog</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Gudrun Norstedt</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Gudrun Norstedt</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1586002</t>
+          <t>https://artportalen.se/Sighting/136990694</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122748168</v>
+        <v>136990655</v>
       </c>
       <c r="B24" t="n">
-        <v>91872</v>
+        <v>96565</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3260,37 +3250,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>2812</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Jenberget NÖ, Vb</t>
+          <t>Gröthällan, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759334</v>
+        <v>759488</v>
       </c>
       <c r="R24" t="n">
-        <v>7074199</v>
+        <v>7074200</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3314,12 +3304,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3334,31 +3334,27 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jessica  Åström</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122748168</t>
+          <t>https://artportalen.se/Sighting/136990655</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130261223</v>
+        <v>136990691</v>
       </c>
       <c r="B25" t="n">
-        <v>91872</v>
+        <v>96565</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3366,34 +3362,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>2812</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>NV Gröthällberget, Vb</t>
+          <t>Gröthällan, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759450</v>
+        <v>759513</v>
       </c>
       <c r="R25" t="n">
-        <v>7074279</v>
+        <v>7074245</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3420,12 +3416,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3436,51 +3442,31 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL25" t="inlineStr">
-        <is>
-          <t>Granlåga knäckt</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga knäckt</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261223</t>
+          <t>https://artportalen.se/Sighting/136990691</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130261224</v>
+        <v>130261232</v>
       </c>
       <c r="B26" t="n">
-        <v>91872</v>
+        <v>92632</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,21 +3474,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3512,10 +3498,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759568</v>
+        <v>759330</v>
       </c>
       <c r="R26" t="n">
-        <v>7074103</v>
+        <v>7074184</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3571,12 +3557,12 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>Äldre granlåga</t>
+          <t>Stående död</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre granlåga</t>
+          <t>Picea abies # Stående död</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3593,13 +3579,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261224</t>
+          <t>https://artportalen.se/Sighting/130261232</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130261225</v>
+        <v>1586002</v>
       </c>
       <c r="B27" t="n">
         <v>91872</v>
@@ -3630,14 +3616,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>NV Gröthällberget, Vb</t>
+          <t>Båtsviksberget, 430 m SSV om, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>759453</v>
+        <v>759505</v>
       </c>
       <c r="R27" t="n">
-        <v>7074313</v>
+        <v>7074277</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3664,12 +3650,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2011-06-05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2011-06-05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3681,47 +3667,37 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL27" t="inlineStr">
-        <is>
-          <t>Tunnare granlåga invid äldre talltorraka</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies # Tunnare granlåga invid äldre talltorraka</t>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Äldre granskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Gudrun Norstedt</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Gudrun Norstedt</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261225</t>
+          <t>https://artportalen.se/Sighting/1586002</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130261226</v>
+        <v>122748168</v>
       </c>
       <c r="B28" t="n">
         <v>91872</v>
@@ -3752,17 +3728,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>NV Gröthällberget, Vb</t>
+          <t>Jenberget NÖ, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>759410</v>
+        <v>759334</v>
       </c>
       <c r="R28" t="n">
-        <v>7074242</v>
+        <v>7074199</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3786,12 +3762,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3802,51 +3778,35 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL28" t="inlineStr">
-        <is>
-          <t>Granlåga rotknäckt</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga rotknäckt</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Jessica  Åström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261226</t>
+          <t>https://artportalen.se/Sighting/122748168</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136990652</v>
+        <v>130261223</v>
       </c>
       <c r="B29" t="n">
-        <v>92076</v>
+        <v>91872</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3874,14 +3834,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gröthällan, Vb</t>
+          <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759401</v>
+        <v>759450</v>
       </c>
       <c r="R29" t="n">
-        <v>7074284</v>
+        <v>7074279</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3908,22 +3868,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3934,31 +3884,51 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>Granlåga knäckt</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga knäckt</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136990652</t>
+          <t>https://artportalen.se/Sighting/130261223</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136990658</v>
+        <v>130261224</v>
       </c>
       <c r="B30" t="n">
-        <v>92076</v>
+        <v>91872</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3986,14 +3956,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gröthällan, Vb</t>
+          <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>759565</v>
+        <v>759568</v>
       </c>
       <c r="R30" t="n">
-        <v>7074114</v>
+        <v>7074103</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4020,22 +3990,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:47</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:47</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4046,31 +4006,51 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>Äldre granlåga</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre granlåga</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136990658</t>
+          <t>https://artportalen.se/Sighting/130261224</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136990669</v>
+        <v>130261225</v>
       </c>
       <c r="B31" t="n">
-        <v>92076</v>
+        <v>91872</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4098,14 +4078,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gröthällan, Vb</t>
+          <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>759555</v>
+        <v>759453</v>
       </c>
       <c r="R31" t="n">
-        <v>7074182</v>
+        <v>7074313</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4132,22 +4112,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>12:53</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>12:53</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4158,31 +4128,51 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>Tunnare granlåga invid äldre talltorraka</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies # Tunnare granlåga invid äldre talltorraka</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136990669</t>
+          <t>https://artportalen.se/Sighting/130261225</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136990683</v>
+        <v>130261226</v>
       </c>
       <c r="B32" t="n">
-        <v>92076</v>
+        <v>91872</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4210,14 +4200,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gröthällan, Vb</t>
+          <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>759438</v>
+        <v>759410</v>
       </c>
       <c r="R32" t="n">
-        <v>7074263</v>
+        <v>7074242</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4244,22 +4234,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:47</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:47</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4270,28 +4250,48 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>Granlåga rotknäckt</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga rotknäckt</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136990683</t>
+          <t>https://artportalen.se/Sighting/130261226</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>136990684</v>
+        <v>136990652</v>
       </c>
       <c r="B33" t="n">
         <v>92076</v>
@@ -4326,10 +4326,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>759449</v>
+        <v>759401</v>
       </c>
       <c r="R33" t="n">
-        <v>7074321</v>
+        <v>7074284</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4356,22 +4356,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4397,57 +4397,54 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136990684</t>
+          <t>https://artportalen.se/Sighting/136990652</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>114558886</v>
+        <v>136990658</v>
       </c>
       <c r="B34" t="n">
-        <v>79327</v>
+        <v>92076</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>300m NO Gröthällberget, Vb</t>
+          <t>Gröthällan, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>759614</v>
+        <v>759565</v>
       </c>
       <c r="R34" t="n">
-        <v>7074148</v>
+        <v>7074114</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4471,12 +4468,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4485,56 +4492,55 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Andreas Drott</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Andreas Drott, Karl-Henrik  Drott</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114558886</t>
+          <t>https://artportalen.se/Sighting/136990658</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>136990648</v>
+        <v>136990669</v>
       </c>
       <c r="B35" t="n">
-        <v>79476</v>
+        <v>92076</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4544,10 +4550,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>759357</v>
+        <v>759555</v>
       </c>
       <c r="R35" t="n">
-        <v>7074202</v>
+        <v>7074182</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4579,7 +4585,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4589,7 +4595,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4615,38 +4621,38 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136990648</t>
+          <t>https://artportalen.se/Sighting/136990669</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>136990653</v>
+        <v>136990683</v>
       </c>
       <c r="B36" t="n">
-        <v>79476</v>
+        <v>92076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4656,10 +4662,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>759430</v>
+        <v>759438</v>
       </c>
       <c r="R36" t="n">
-        <v>7074290</v>
+        <v>7074263</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4686,22 +4692,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4727,38 +4733,38 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136990653</t>
+          <t>https://artportalen.se/Sighting/136990683</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>136990657</v>
+        <v>136990684</v>
       </c>
       <c r="B37" t="n">
-        <v>79476</v>
+        <v>92076</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4768,10 +4774,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>759532</v>
+        <v>759449</v>
       </c>
       <c r="R37" t="n">
-        <v>7074133</v>
+        <v>7074321</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4798,22 +4804,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4839,38 +4845,38 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136990657</t>
+          <t>https://artportalen.se/Sighting/136990684</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>136990664</v>
+        <v>137016885</v>
       </c>
       <c r="B38" t="n">
-        <v>79476</v>
+        <v>92076</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4880,10 +4886,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>759609</v>
+        <v>759380</v>
       </c>
       <c r="R38" t="n">
-        <v>7074093</v>
+        <v>7074188</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4910,22 +4916,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4945,44 +4951,44 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Felix Gustafsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136990664</t>
+          <t>https://artportalen.se/Sighting/137016885</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>136990665</v>
+        <v>137016889</v>
       </c>
       <c r="B39" t="n">
-        <v>79476</v>
+        <v>92076</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4992,10 +4998,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>759610</v>
+        <v>759510</v>
       </c>
       <c r="R39" t="n">
-        <v>7074115</v>
+        <v>7074288</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5022,22 +5028,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5057,44 +5063,44 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Felix Gustafsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136990665</t>
+          <t>https://artportalen.se/Sighting/137016889</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136990667</v>
+        <v>137017883</v>
       </c>
       <c r="B40" t="n">
-        <v>79476</v>
+        <v>92076</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5104,10 +5110,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>759580</v>
+        <v>759523</v>
       </c>
       <c r="R40" t="n">
-        <v>7074138</v>
+        <v>7074301</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5134,22 +5140,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5164,49 +5170,49 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Alva Danielsson, Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136990667</t>
+          <t>https://artportalen.se/Sighting/137017883</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>136990679</v>
+        <v>137017885</v>
       </c>
       <c r="B41" t="n">
-        <v>79476</v>
+        <v>92076</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5216,10 +5222,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>759412</v>
+        <v>759590</v>
       </c>
       <c r="R41" t="n">
-        <v>7074157</v>
+        <v>7074168</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5246,22 +5252,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5276,27 +5282,27 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Alva Danielsson, Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136990679</t>
+          <t>https://artportalen.se/Sighting/137017885</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>136990680</v>
+        <v>114558886</v>
       </c>
       <c r="B42" t="n">
-        <v>79476</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5322,19 +5328,22 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Gröthällan, Vb</t>
+          <t>300m NO Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>759435</v>
+        <v>759614</v>
       </c>
       <c r="R42" t="n">
-        <v>7074157</v>
+        <v>7074148</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5358,22 +5367,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>14:29</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>14:29</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5382,30 +5381,31 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Andreas Drott</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Andreas Drott, Karl-Henrik  Drott</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136990680</t>
+          <t>https://artportalen.se/Sighting/114558886</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>136990686</v>
+        <v>136990648</v>
       </c>
       <c r="B43" t="n">
         <v>79476</v>
@@ -5440,10 +5440,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>759454</v>
+        <v>759357</v>
       </c>
       <c r="R43" t="n">
-        <v>7074302</v>
+        <v>7074202</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5470,22 +5470,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5511,13 +5511,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136990686</t>
+          <t>https://artportalen.se/Sighting/136990648</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>136990688</v>
+        <v>136990653</v>
       </c>
       <c r="B44" t="n">
         <v>79476</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>759542</v>
+        <v>759430</v>
       </c>
       <c r="R44" t="n">
-        <v>7074337</v>
+        <v>7074290</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5582,22 +5582,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5623,13 +5623,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136990688</t>
+          <t>https://artportalen.se/Sighting/136990653</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>136990690</v>
+        <v>136990657</v>
       </c>
       <c r="B45" t="n">
         <v>79476</v>
@@ -5664,10 +5664,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>759513</v>
+        <v>759532</v>
       </c>
       <c r="R45" t="n">
-        <v>7074242</v>
+        <v>7074133</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5694,22 +5694,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5735,13 +5735,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136990690</t>
+          <t>https://artportalen.se/Sighting/136990657</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>136990692</v>
+        <v>136990664</v>
       </c>
       <c r="B46" t="n">
         <v>79476</v>
@@ -5776,10 +5776,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>759539</v>
+        <v>759609</v>
       </c>
       <c r="R46" t="n">
-        <v>7074223</v>
+        <v>7074093</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5806,22 +5806,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5847,56 +5847,51 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136990692</t>
+          <t>https://artportalen.se/Sighting/136990664</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130261235</v>
+        <v>136990665</v>
       </c>
       <c r="B47" t="n">
-        <v>57950</v>
+        <v>79476</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>NV Gröthällberget, Vb</t>
+          <t>Gröthällan, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>759616</v>
+        <v>759610</v>
       </c>
       <c r="R47" t="n">
-        <v>7074094</v>
+        <v>7074115</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5923,12 +5918,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5939,91 +5944,66 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL47" t="inlineStr">
-        <is>
-          <t>Granhögstubbe knäckt</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe knäckt</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261235</t>
+          <t>https://artportalen.se/Sighting/136990665</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130261236</v>
+        <v>136990667</v>
       </c>
       <c r="B48" t="n">
-        <v>57950</v>
+        <v>79476</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>NV Gröthällberget, Vb</t>
+          <t>Gröthällan, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>759588</v>
+        <v>759580</v>
       </c>
       <c r="R48" t="n">
-        <v>7074157</v>
+        <v>7074138</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6050,12 +6030,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6066,91 +6056,66 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL48" t="inlineStr">
-        <is>
-          <t>Granhögstubbe grov, knäckt</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe grov, knäckt</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261236</t>
+          <t>https://artportalen.se/Sighting/136990667</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130261237</v>
+        <v>136990679</v>
       </c>
       <c r="B49" t="n">
-        <v>57950</v>
+        <v>79476</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>NV Gröthällberget, Vb</t>
+          <t>Gröthällan, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>759528</v>
+        <v>759412</v>
       </c>
       <c r="R49" t="n">
-        <v>7074150</v>
+        <v>7074157</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6177,17 +6142,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Högt upp</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6198,91 +6168,66 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL49" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Picea abies # Levande</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261237</t>
+          <t>https://artportalen.se/Sighting/136990679</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130261238</v>
+        <v>136990680</v>
       </c>
       <c r="B50" t="n">
-        <v>57950</v>
+        <v>79476</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>NV Gröthällberget, Vb</t>
+          <t>Gröthällan, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>759413</v>
+        <v>759435</v>
       </c>
       <c r="R50" t="n">
-        <v>7074262</v>
+        <v>7074157</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6309,17 +6254,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Vid basen</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6330,91 +6280,66 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL50" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Picea abies # Levande</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261238</t>
+          <t>https://artportalen.se/Sighting/136990680</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130261239</v>
+        <v>136990686</v>
       </c>
       <c r="B51" t="n">
-        <v>57950</v>
+        <v>79476</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>NV Gröthällberget, Vb</t>
+          <t>Gröthällan, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>759521</v>
+        <v>759454</v>
       </c>
       <c r="R51" t="n">
-        <v>7074165</v>
+        <v>7074302</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6441,12 +6366,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6457,91 +6392,66 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL51" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Picea abies # Levande</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261239</t>
+          <t>https://artportalen.se/Sighting/136990686</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130261240</v>
+        <v>136990688</v>
       </c>
       <c r="B52" t="n">
-        <v>57950</v>
+        <v>79476</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>NV Gröthällberget, Vb</t>
+          <t>Gröthällan, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>759411</v>
+        <v>759542</v>
       </c>
       <c r="R52" t="n">
-        <v>7074135</v>
+        <v>7074337</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6568,12 +6478,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6584,91 +6504,66 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL52" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Picea abies # Levande</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261240</t>
+          <t>https://artportalen.se/Sighting/136990688</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130261241</v>
+        <v>136990690</v>
       </c>
       <c r="B53" t="n">
-        <v>57950</v>
+        <v>79476</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>NV Gröthällberget, Vb</t>
+          <t>Gröthällan, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>759358</v>
+        <v>759513</v>
       </c>
       <c r="R53" t="n">
-        <v>7074193</v>
+        <v>7074242</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6695,12 +6590,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6711,91 +6616,66 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL53" t="inlineStr">
-        <is>
-          <t>Granlåga, knäckt</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga, knäckt</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261241</t>
+          <t>https://artportalen.se/Sighting/136990690</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130261242</v>
+        <v>136990692</v>
       </c>
       <c r="B54" t="n">
-        <v>57950</v>
+        <v>79476</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>NV Gröthällberget, Vb</t>
+          <t>Gröthällan, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>759521</v>
+        <v>759539</v>
       </c>
       <c r="R54" t="n">
-        <v>7074133</v>
+        <v>7074223</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6822,17 +6702,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Vid basen</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6843,91 +6728,66 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL54" t="inlineStr">
-        <is>
-          <t>Knäckt gran</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Picea abies # Knäckt gran</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261242</t>
+          <t>https://artportalen.se/Sighting/136990692</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130261243</v>
+        <v>137016888</v>
       </c>
       <c r="B55" t="n">
-        <v>57950</v>
+        <v>79476</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>NV Gröthällberget, Vb</t>
+          <t>Gröthällan, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>759457</v>
+        <v>759477</v>
       </c>
       <c r="R55" t="n">
-        <v>7074149</v>
+        <v>7074240</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6954,17 +6814,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Kåda</t>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6975,81 +6840,69 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261243</t>
+          <t>https://artportalen.se/Sighting/137016888</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>136990659</v>
+        <v>137017881</v>
       </c>
       <c r="B56" t="n">
-        <v>58005</v>
+        <v>79476</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Gröthällan, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>759558</v>
+        <v>759438</v>
       </c>
       <c r="R56" t="n">
-        <v>7074114</v>
+        <v>7074303</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7076,22 +6929,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7100,50 +6953,51 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Alva Danielsson, Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136990659</t>
+          <t>https://artportalen.se/Sighting/137017881</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130261228</v>
+        <v>130261235</v>
       </c>
       <c r="B57" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -7152,24 +7006,21 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>759417</v>
+        <v>759616</v>
       </c>
       <c r="R57" t="n">
-        <v>7074118</v>
+        <v>7074094</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7204,11 +7055,6 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7230,12 +7076,12 @@
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>Stående död</t>
+          <t>Granhögstubbe knäckt</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död</t>
+          <t>Picea abies # Granhögstubbe knäckt</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7252,33 +7098,33 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261228</t>
+          <t>https://artportalen.se/Sighting/130261235</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130261231</v>
+        <v>130261236</v>
       </c>
       <c r="B58" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -7298,10 +7144,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>759348</v>
+        <v>759588</v>
       </c>
       <c r="R58" t="n">
-        <v>7074185</v>
+        <v>7074157</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7336,11 +7182,6 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack på granlåga</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7362,12 +7203,12 @@
       </c>
       <c r="AL58" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granhögstubbe grov, knäckt</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Granhögstubbe grov, knäckt</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7384,33 +7225,33 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261231</t>
+          <t>https://artportalen.se/Sighting/130261236</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>136990670</v>
+        <v>130261237</v>
       </c>
       <c r="B59" t="n">
-        <v>58008</v>
+        <v>57950</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -7419,24 +7260,21 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gröthällan, Vb</t>
+          <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>759545</v>
+        <v>759528</v>
       </c>
       <c r="R59" t="n">
-        <v>7074163</v>
+        <v>7074150</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7463,27 +7301,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>12:55</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>12:55</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Gammalt ringhack</t>
+          <t>Högt upp</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7494,31 +7322,51 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL59" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Picea abies # Levande</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136990670</t>
+          <t>https://artportalen.se/Sighting/130261237</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130261249</v>
+        <v>130261238</v>
       </c>
       <c r="B60" t="n">
-        <v>58327</v>
+        <v>57950</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7526,16 +7374,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7544,24 +7392,21 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>759466</v>
+        <v>759413</v>
       </c>
       <c r="R60" t="n">
-        <v>7074152</v>
+        <v>7074262</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7591,19 +7436,14 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>10:40</t>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Vid basen</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7614,6 +7454,26 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL60" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies # Levande</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7629,59 +7489,56 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261249</t>
+          <t>https://artportalen.se/Sighting/130261238</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130261233</v>
+        <v>130261239</v>
       </c>
       <c r="B61" t="n">
-        <v>58114</v>
+        <v>57950</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>759425</v>
+        <v>759521</v>
       </c>
       <c r="R61" t="n">
-        <v>7074122</v>
+        <v>7074165</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7711,21 +7568,11 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7734,6 +7581,26 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL61" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Picea abies # Levande</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7749,63 +7616,56 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261233</t>
+          <t>https://artportalen.se/Sighting/130261239</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130261234</v>
+        <v>130261240</v>
       </c>
       <c r="B62" t="n">
-        <v>58114</v>
+        <v>57950</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>759386</v>
+        <v>759411</v>
       </c>
       <c r="R62" t="n">
-        <v>7074195</v>
+        <v>7074135</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7835,21 +7695,11 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7858,6 +7708,26 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL62" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Picea abies # Levande</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7873,51 +7743,56 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130261234</t>
+          <t>https://artportalen.se/Sighting/130261240</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>136990660</v>
+        <v>130261241</v>
       </c>
       <c r="B63" t="n">
-        <v>58169</v>
+        <v>57950</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gröthällan, Vb</t>
+          <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>759548</v>
+        <v>759358</v>
       </c>
       <c r="R63" t="n">
-        <v>7074112</v>
+        <v>7074193</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7944,22 +7819,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>11:51</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>11:51</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7970,66 +7835,91 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL63" t="inlineStr">
+        <is>
+          <t>Granlåga, knäckt</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga, knäckt</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136990660</t>
+          <t>https://artportalen.se/Sighting/130261241</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>136990668</v>
+        <v>130261242</v>
       </c>
       <c r="B64" t="n">
-        <v>99353</v>
+        <v>57950</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Gröthällan, Vb</t>
+          <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>759580</v>
+        <v>759521</v>
       </c>
       <c r="R64" t="n">
-        <v>7074146</v>
+        <v>7074133</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -8056,22 +7946,17 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>12:44</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>12:44</t>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Vid basen</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8082,20 +7967,1371 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL64" t="inlineStr">
+        <is>
+          <t>Knäckt gran</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Picea abies # Knäckt gran</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261242</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>130261243</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>759457</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7074149</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Kåda</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261243</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>136990659</v>
+      </c>
+      <c r="B66" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Gröthällan, Vb</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>759558</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7074114</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136990659</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>130261228</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>759417</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7074118</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL67" t="inlineStr">
+        <is>
+          <t>Stående död</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261228</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>130261231</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>759348</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7074185</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack på granlåga</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL68" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261231</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>136990670</v>
+      </c>
+      <c r="B69" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Gröthällan, Vb</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>759545</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7074163</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Gammalt ringhack</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136990670</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>130261249</v>
+      </c>
+      <c r="B70" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>759466</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7074152</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261249</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>130261233</v>
+      </c>
+      <c r="B71" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>759425</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7074122</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261233</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>130261234</v>
+      </c>
+      <c r="B72" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>759386</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7074195</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261234</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>136990660</v>
+      </c>
+      <c r="B73" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Gröthällan, Vb</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>759548</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7074112</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136990660</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>137017878</v>
+      </c>
+      <c r="B74" t="n">
+        <v>111332</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Gröthällan, Vb</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>759460</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7074175</v>
+      </c>
+      <c r="S74" t="n">
+        <v>1</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137017878</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>136990668</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Gröthällan, Vb</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>759580</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7074146</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136990668</t>
         </is>
@@ -8166,6 +9402,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>137016886</v>
       </c>
       <c r="B3" t="n">
-        <v>92063</v>
+        <v>92065</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>137016887</v>
       </c>
       <c r="B4" t="n">
-        <v>92063</v>
+        <v>92065</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136990661</v>
       </c>
       <c r="B11" t="n">
-        <v>92109</v>
+        <v>92111</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>136990666</v>
       </c>
       <c r="B12" t="n">
-        <v>92109</v>
+        <v>92111</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136990671</v>
       </c>
       <c r="B13" t="n">
-        <v>92109</v>
+        <v>92111</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>136990685</v>
       </c>
       <c r="B14" t="n">
-        <v>92109</v>
+        <v>92111</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>137017880</v>
       </c>
       <c r="B15" t="n">
-        <v>92109</v>
+        <v>92111</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>137017886</v>
       </c>
       <c r="B16" t="n">
-        <v>92109</v>
+        <v>92111</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>136990687</v>
       </c>
       <c r="B20" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>136990689</v>
       </c>
       <c r="B21" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>136990656</v>
       </c>
       <c r="B22" t="n">
-        <v>96568</v>
+        <v>96574</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>136990694</v>
       </c>
       <c r="B23" t="n">
-        <v>96568</v>
+        <v>96574</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136990655</v>
       </c>
       <c r="B24" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>136990691</v>
       </c>
       <c r="B25" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>136990652</v>
       </c>
       <c r="B33" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>136990658</v>
       </c>
       <c r="B34" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>136990669</v>
       </c>
       <c r="B35" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>136990683</v>
       </c>
       <c r="B36" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>136990684</v>
       </c>
       <c r="B37" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>137016885</v>
       </c>
       <c r="B38" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>137016889</v>
       </c>
       <c r="B39" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>137017883</v>
       </c>
       <c r="B40" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>137017885</v>
       </c>
       <c r="B41" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>136990648</v>
       </c>
       <c r="B43" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>136990653</v>
       </c>
       <c r="B44" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>136990657</v>
       </c>
       <c r="B45" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>136990664</v>
       </c>
       <c r="B46" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>136990665</v>
       </c>
       <c r="B47" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>136990667</v>
       </c>
       <c r="B48" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>136990679</v>
       </c>
       <c r="B49" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
         <v>136990680</v>
       </c>
       <c r="B50" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>136990686</v>
       </c>
       <c r="B51" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>136990688</v>
       </c>
       <c r="B52" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>136990690</v>
       </c>
       <c r="B53" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>136990692</v>
       </c>
       <c r="B54" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>137016888</v>
       </c>
       <c r="B55" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         <v>137017881</v>
       </c>
       <c r="B56" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>137017878</v>
       </c>
       <c r="B74" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>136990668</v>
       </c>
       <c r="B75" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>137016886</v>
       </c>
       <c r="B3" t="n">
-        <v>92065</v>
+        <v>92067</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>137016887</v>
       </c>
       <c r="B4" t="n">
-        <v>92065</v>
+        <v>92067</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136990661</v>
       </c>
       <c r="B11" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>136990666</v>
       </c>
       <c r="B12" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136990671</v>
       </c>
       <c r="B13" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>136990685</v>
       </c>
       <c r="B14" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>137017880</v>
       </c>
       <c r="B15" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>137017886</v>
       </c>
       <c r="B16" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>136990687</v>
       </c>
       <c r="B20" t="n">
-        <v>92126</v>
+        <v>92128</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>136990689</v>
       </c>
       <c r="B21" t="n">
-        <v>92126</v>
+        <v>92128</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>136990656</v>
       </c>
       <c r="B22" t="n">
-        <v>96574</v>
+        <v>96576</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>136990694</v>
       </c>
       <c r="B23" t="n">
-        <v>96574</v>
+        <v>96576</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136990655</v>
       </c>
       <c r="B24" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>136990691</v>
       </c>
       <c r="B25" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>136990652</v>
       </c>
       <c r="B33" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>136990658</v>
       </c>
       <c r="B34" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>136990669</v>
       </c>
       <c r="B35" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>136990683</v>
       </c>
       <c r="B36" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>136990684</v>
       </c>
       <c r="B37" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>137016885</v>
       </c>
       <c r="B38" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>137016889</v>
       </c>
       <c r="B39" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>137017883</v>
       </c>
       <c r="B40" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>137017885</v>
       </c>
       <c r="B41" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>136990648</v>
       </c>
       <c r="B43" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>136990653</v>
       </c>
       <c r="B44" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>136990657</v>
       </c>
       <c r="B45" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>136990664</v>
       </c>
       <c r="B46" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>136990665</v>
       </c>
       <c r="B47" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>136990667</v>
       </c>
       <c r="B48" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>136990679</v>
       </c>
       <c r="B49" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
         <v>136990680</v>
       </c>
       <c r="B50" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>136990686</v>
       </c>
       <c r="B51" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>136990688</v>
       </c>
       <c r="B52" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>136990690</v>
       </c>
       <c r="B53" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>136990692</v>
       </c>
       <c r="B54" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>137016888</v>
       </c>
       <c r="B55" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         <v>137017881</v>
       </c>
       <c r="B56" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>137017878</v>
       </c>
       <c r="B74" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>136990668</v>
       </c>
       <c r="B75" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>137016886</v>
       </c>
       <c r="B3" t="n">
-        <v>92067</v>
+        <v>92068</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>137016887</v>
       </c>
       <c r="B4" t="n">
-        <v>92067</v>
+        <v>92068</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136990661</v>
       </c>
       <c r="B11" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>136990666</v>
       </c>
       <c r="B12" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136990671</v>
       </c>
       <c r="B13" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>136990685</v>
       </c>
       <c r="B14" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>137017880</v>
       </c>
       <c r="B15" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>137017886</v>
       </c>
       <c r="B16" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>136990687</v>
       </c>
       <c r="B20" t="n">
-        <v>92128</v>
+        <v>92129</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>136990689</v>
       </c>
       <c r="B21" t="n">
-        <v>92128</v>
+        <v>92129</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>136990656</v>
       </c>
       <c r="B22" t="n">
-        <v>96576</v>
+        <v>96577</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>136990694</v>
       </c>
       <c r="B23" t="n">
-        <v>96576</v>
+        <v>96577</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136990655</v>
       </c>
       <c r="B24" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>136990691</v>
       </c>
       <c r="B25" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>136990652</v>
       </c>
       <c r="B33" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>136990658</v>
       </c>
       <c r="B34" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>136990669</v>
       </c>
       <c r="B35" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>136990683</v>
       </c>
       <c r="B36" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>136990684</v>
       </c>
       <c r="B37" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>137016885</v>
       </c>
       <c r="B38" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>137016889</v>
       </c>
       <c r="B39" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>137017883</v>
       </c>
       <c r="B40" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>137017885</v>
       </c>
       <c r="B41" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>136990648</v>
       </c>
       <c r="B43" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>136990653</v>
       </c>
       <c r="B44" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>136990657</v>
       </c>
       <c r="B45" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>136990664</v>
       </c>
       <c r="B46" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>136990665</v>
       </c>
       <c r="B47" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>136990667</v>
       </c>
       <c r="B48" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>136990679</v>
       </c>
       <c r="B49" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
         <v>136990680</v>
       </c>
       <c r="B50" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>136990686</v>
       </c>
       <c r="B51" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>136990688</v>
       </c>
       <c r="B52" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>136990690</v>
       </c>
       <c r="B53" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>136990692</v>
       </c>
       <c r="B54" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>137016888</v>
       </c>
       <c r="B55" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         <v>137017881</v>
       </c>
       <c r="B56" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>137017878</v>
       </c>
       <c r="B74" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>136990668</v>
       </c>
       <c r="B75" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>137016886</v>
       </c>
       <c r="B3" t="n">
-        <v>92068</v>
+        <v>92074</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>137016887</v>
       </c>
       <c r="B4" t="n">
-        <v>92068</v>
+        <v>92074</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136990661</v>
       </c>
       <c r="B11" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>136990666</v>
       </c>
       <c r="B12" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136990671</v>
       </c>
       <c r="B13" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>136990685</v>
       </c>
       <c r="B14" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>137017880</v>
       </c>
       <c r="B15" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>137017886</v>
       </c>
       <c r="B16" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>136990687</v>
       </c>
       <c r="B20" t="n">
-        <v>92129</v>
+        <v>92135</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>136990689</v>
       </c>
       <c r="B21" t="n">
-        <v>92129</v>
+        <v>92135</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>136990656</v>
       </c>
       <c r="B22" t="n">
-        <v>96577</v>
+        <v>96583</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>136990694</v>
       </c>
       <c r="B23" t="n">
-        <v>96577</v>
+        <v>96583</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136990655</v>
       </c>
       <c r="B24" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>136990691</v>
       </c>
       <c r="B25" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>136990652</v>
       </c>
       <c r="B33" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>136990658</v>
       </c>
       <c r="B34" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>136990669</v>
       </c>
       <c r="B35" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>136990683</v>
       </c>
       <c r="B36" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>136990684</v>
       </c>
       <c r="B37" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>137016885</v>
       </c>
       <c r="B38" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>137016889</v>
       </c>
       <c r="B39" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>137017883</v>
       </c>
       <c r="B40" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>137017885</v>
       </c>
       <c r="B41" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>137017878</v>
       </c>
       <c r="B74" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>136990668</v>
       </c>
       <c r="B75" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>137016886</v>
       </c>
       <c r="B3" t="n">
-        <v>92074</v>
+        <v>92078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>137016887</v>
       </c>
       <c r="B4" t="n">
-        <v>92074</v>
+        <v>92078</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136990661</v>
       </c>
       <c r="B11" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>136990666</v>
       </c>
       <c r="B12" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136990671</v>
       </c>
       <c r="B13" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>136990685</v>
       </c>
       <c r="B14" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>137017880</v>
       </c>
       <c r="B15" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>137017886</v>
       </c>
       <c r="B16" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>136990687</v>
       </c>
       <c r="B20" t="n">
-        <v>92135</v>
+        <v>92139</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>136990689</v>
       </c>
       <c r="B21" t="n">
-        <v>92135</v>
+        <v>92139</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>136990656</v>
       </c>
       <c r="B22" t="n">
-        <v>96583</v>
+        <v>96587</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>136990694</v>
       </c>
       <c r="B23" t="n">
-        <v>96583</v>
+        <v>96587</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136990655</v>
       </c>
       <c r="B24" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>136990691</v>
       </c>
       <c r="B25" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>136990652</v>
       </c>
       <c r="B33" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>136990658</v>
       </c>
       <c r="B34" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>136990669</v>
       </c>
       <c r="B35" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>136990683</v>
       </c>
       <c r="B36" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>136990684</v>
       </c>
       <c r="B37" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>137016885</v>
       </c>
       <c r="B38" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>137016889</v>
       </c>
       <c r="B39" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>137017883</v>
       </c>
       <c r="B40" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>137017885</v>
       </c>
       <c r="B41" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>136990648</v>
       </c>
       <c r="B43" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>136990653</v>
       </c>
       <c r="B44" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>136990657</v>
       </c>
       <c r="B45" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>136990664</v>
       </c>
       <c r="B46" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>136990665</v>
       </c>
       <c r="B47" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>136990667</v>
       </c>
       <c r="B48" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>136990679</v>
       </c>
       <c r="B49" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
         <v>136990680</v>
       </c>
       <c r="B50" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>136990686</v>
       </c>
       <c r="B51" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>136990688</v>
       </c>
       <c r="B52" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>136990690</v>
       </c>
       <c r="B53" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>136990692</v>
       </c>
       <c r="B54" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>137016888</v>
       </c>
       <c r="B55" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         <v>137017881</v>
       </c>
       <c r="B56" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>137017878</v>
       </c>
       <c r="B74" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>136990668</v>
       </c>
       <c r="B75" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -3018,7 +3018,7 @@
         <v>136990656</v>
       </c>
       <c r="B22" t="n">
-        <v>96587</v>
+        <v>96589</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>136990694</v>
       </c>
       <c r="B23" t="n">
-        <v>96587</v>
+        <v>96589</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136990655</v>
       </c>
       <c r="B24" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>136990691</v>
       </c>
       <c r="B25" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>137017878</v>
       </c>
       <c r="B74" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>136990668</v>
       </c>
       <c r="B75" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>137016886</v>
       </c>
       <c r="B3" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>137016887</v>
       </c>
       <c r="B4" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136990661</v>
       </c>
       <c r="B11" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>136990666</v>
       </c>
       <c r="B12" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136990671</v>
       </c>
       <c r="B13" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>136990685</v>
       </c>
       <c r="B14" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>137017880</v>
       </c>
       <c r="B15" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>137017886</v>
       </c>
       <c r="B16" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>136990687</v>
       </c>
       <c r="B20" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>136990689</v>
       </c>
       <c r="B21" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>136990656</v>
       </c>
       <c r="B22" t="n">
-        <v>96589</v>
+        <v>96591</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>136990694</v>
       </c>
       <c r="B23" t="n">
-        <v>96589</v>
+        <v>96591</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136990655</v>
       </c>
       <c r="B24" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>136990691</v>
       </c>
       <c r="B25" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>136990652</v>
       </c>
       <c r="B33" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>136990658</v>
       </c>
       <c r="B34" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>136990669</v>
       </c>
       <c r="B35" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>136990683</v>
       </c>
       <c r="B36" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>136990684</v>
       </c>
       <c r="B37" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>137016885</v>
       </c>
       <c r="B38" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>137016889</v>
       </c>
       <c r="B39" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>137017883</v>
       </c>
       <c r="B40" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>137017885</v>
       </c>
       <c r="B41" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>136990648</v>
       </c>
       <c r="B43" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>136990653</v>
       </c>
       <c r="B44" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>136990657</v>
       </c>
       <c r="B45" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>136990664</v>
       </c>
       <c r="B46" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>136990665</v>
       </c>
       <c r="B47" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>136990667</v>
       </c>
       <c r="B48" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>136990679</v>
       </c>
       <c r="B49" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
         <v>136990680</v>
       </c>
       <c r="B50" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>136990686</v>
       </c>
       <c r="B51" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>136990688</v>
       </c>
       <c r="B52" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>136990690</v>
       </c>
       <c r="B53" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>136990692</v>
       </c>
       <c r="B54" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>137016888</v>
       </c>
       <c r="B55" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         <v>137017881</v>
       </c>
       <c r="B56" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>137017878</v>
       </c>
       <c r="B74" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>136990668</v>
       </c>
       <c r="B75" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>137016886</v>
       </c>
       <c r="B3" t="n">
-        <v>92080</v>
+        <v>92093</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>137016887</v>
       </c>
       <c r="B4" t="n">
-        <v>92080</v>
+        <v>92093</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136990661</v>
       </c>
       <c r="B11" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>136990666</v>
       </c>
       <c r="B12" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136990671</v>
       </c>
       <c r="B13" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>136990685</v>
       </c>
       <c r="B14" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>137017880</v>
       </c>
       <c r="B15" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>137017886</v>
       </c>
       <c r="B16" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>136990687</v>
       </c>
       <c r="B20" t="n">
-        <v>92141</v>
+        <v>92154</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>136990689</v>
       </c>
       <c r="B21" t="n">
-        <v>92141</v>
+        <v>92154</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>136990656</v>
       </c>
       <c r="B22" t="n">
-        <v>96591</v>
+        <v>96604</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>136990694</v>
       </c>
       <c r="B23" t="n">
-        <v>96591</v>
+        <v>96604</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136990655</v>
       </c>
       <c r="B24" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>136990691</v>
       </c>
       <c r="B25" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>136990652</v>
       </c>
       <c r="B33" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>136990658</v>
       </c>
       <c r="B34" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>136990669</v>
       </c>
       <c r="B35" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>136990683</v>
       </c>
       <c r="B36" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>136990684</v>
       </c>
       <c r="B37" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>137016885</v>
       </c>
       <c r="B38" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>137016889</v>
       </c>
       <c r="B39" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>137017883</v>
       </c>
       <c r="B40" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>137017885</v>
       </c>
       <c r="B41" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>136990648</v>
       </c>
       <c r="B43" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>136990653</v>
       </c>
       <c r="B44" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>136990657</v>
       </c>
       <c r="B45" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>136990664</v>
       </c>
       <c r="B46" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>136990665</v>
       </c>
       <c r="B47" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>136990667</v>
       </c>
       <c r="B48" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>136990679</v>
       </c>
       <c r="B49" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
         <v>136990680</v>
       </c>
       <c r="B50" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>136990686</v>
       </c>
       <c r="B51" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>136990688</v>
       </c>
       <c r="B52" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>136990690</v>
       </c>
       <c r="B53" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>136990692</v>
       </c>
       <c r="B54" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>137016888</v>
       </c>
       <c r="B55" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         <v>137017881</v>
       </c>
       <c r="B56" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>136990659</v>
       </c>
       <c r="B66" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>136990670</v>
       </c>
       <c r="B69" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         <v>136990660</v>
       </c>
       <c r="B73" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>137017878</v>
       </c>
       <c r="B74" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>136990668</v>
       </c>
       <c r="B75" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>137016886</v>
       </c>
       <c r="B3" t="n">
-        <v>92093</v>
+        <v>92095</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>137016887</v>
       </c>
       <c r="B4" t="n">
-        <v>92093</v>
+        <v>92095</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136990661</v>
       </c>
       <c r="B11" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>136990666</v>
       </c>
       <c r="B12" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136990671</v>
       </c>
       <c r="B13" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>136990685</v>
       </c>
       <c r="B14" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>137017880</v>
       </c>
       <c r="B15" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>137017886</v>
       </c>
       <c r="B16" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>136990687</v>
       </c>
       <c r="B20" t="n">
-        <v>92154</v>
+        <v>92156</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>136990689</v>
       </c>
       <c r="B21" t="n">
-        <v>92154</v>
+        <v>92156</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>136990656</v>
       </c>
       <c r="B22" t="n">
-        <v>96604</v>
+        <v>96606</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>136990694</v>
       </c>
       <c r="B23" t="n">
-        <v>96604</v>
+        <v>96606</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136990655</v>
       </c>
       <c r="B24" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>136990691</v>
       </c>
       <c r="B25" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>136990652</v>
       </c>
       <c r="B33" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>136990658</v>
       </c>
       <c r="B34" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>136990669</v>
       </c>
       <c r="B35" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>136990683</v>
       </c>
       <c r="B36" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>136990684</v>
       </c>
       <c r="B37" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>137016885</v>
       </c>
       <c r="B38" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>137016889</v>
       </c>
       <c r="B39" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>137017883</v>
       </c>
       <c r="B40" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>137017885</v>
       </c>
       <c r="B41" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>136990648</v>
       </c>
       <c r="B43" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>136990653</v>
       </c>
       <c r="B44" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>136990657</v>
       </c>
       <c r="B45" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>136990664</v>
       </c>
       <c r="B46" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>136990665</v>
       </c>
       <c r="B47" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>136990667</v>
       </c>
       <c r="B48" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>136990679</v>
       </c>
       <c r="B49" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
         <v>136990680</v>
       </c>
       <c r="B50" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>136990686</v>
       </c>
       <c r="B51" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>136990688</v>
       </c>
       <c r="B52" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>136990690</v>
       </c>
       <c r="B53" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>136990692</v>
       </c>
       <c r="B54" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>137016888</v>
       </c>
       <c r="B55" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         <v>137017881</v>
       </c>
       <c r="B56" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>136990659</v>
       </c>
       <c r="B66" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>136990670</v>
       </c>
       <c r="B69" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         <v>136990660</v>
       </c>
       <c r="B73" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>137017878</v>
       </c>
       <c r="B74" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>136990668</v>
       </c>
       <c r="B75" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -8545,11 +8545,7 @@
       <c r="I69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>137016886</v>
       </c>
       <c r="B3" t="n">
-        <v>92095</v>
+        <v>92098</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>137016887</v>
       </c>
       <c r="B4" t="n">
-        <v>92095</v>
+        <v>92098</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136990661</v>
       </c>
       <c r="B11" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>136990666</v>
       </c>
       <c r="B12" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136990671</v>
       </c>
       <c r="B13" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>136990685</v>
       </c>
       <c r="B14" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>137017880</v>
       </c>
       <c r="B15" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>137017886</v>
       </c>
       <c r="B16" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>136990687</v>
       </c>
       <c r="B20" t="n">
-        <v>92156</v>
+        <v>92159</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>136990689</v>
       </c>
       <c r="B21" t="n">
-        <v>92156</v>
+        <v>92159</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>136990656</v>
       </c>
       <c r="B22" t="n">
-        <v>96606</v>
+        <v>96609</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>136990694</v>
       </c>
       <c r="B23" t="n">
-        <v>96606</v>
+        <v>96609</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136990655</v>
       </c>
       <c r="B24" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>136990691</v>
       </c>
       <c r="B25" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>136990652</v>
       </c>
       <c r="B33" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>136990658</v>
       </c>
       <c r="B34" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>136990669</v>
       </c>
       <c r="B35" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>136990683</v>
       </c>
       <c r="B36" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>136990684</v>
       </c>
       <c r="B37" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>137016885</v>
       </c>
       <c r="B38" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>137016889</v>
       </c>
       <c r="B39" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>137017883</v>
       </c>
       <c r="B40" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>137017885</v>
       </c>
       <c r="B41" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>137017878</v>
       </c>
       <c r="B74" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>136990668</v>
       </c>
       <c r="B75" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>137016886</v>
       </c>
       <c r="B3" t="n">
-        <v>92098</v>
+        <v>92108</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>137016887</v>
       </c>
       <c r="B4" t="n">
-        <v>92098</v>
+        <v>92108</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136990661</v>
       </c>
       <c r="B11" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>136990666</v>
       </c>
       <c r="B12" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136990671</v>
       </c>
       <c r="B13" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>136990685</v>
       </c>
       <c r="B14" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>137017880</v>
       </c>
       <c r="B15" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>137017886</v>
       </c>
       <c r="B16" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>136990687</v>
       </c>
       <c r="B20" t="n">
-        <v>92159</v>
+        <v>92169</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>136990689</v>
       </c>
       <c r="B21" t="n">
-        <v>92159</v>
+        <v>92169</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>136990656</v>
       </c>
       <c r="B22" t="n">
-        <v>96609</v>
+        <v>96619</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>136990694</v>
       </c>
       <c r="B23" t="n">
-        <v>96609</v>
+        <v>96619</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136990655</v>
       </c>
       <c r="B24" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>136990691</v>
       </c>
       <c r="B25" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>136990652</v>
       </c>
       <c r="B33" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>136990658</v>
       </c>
       <c r="B34" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>136990669</v>
       </c>
       <c r="B35" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>136990683</v>
       </c>
       <c r="B36" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>136990684</v>
       </c>
       <c r="B37" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>137016885</v>
       </c>
       <c r="B38" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>137016889</v>
       </c>
       <c r="B39" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>137017883</v>
       </c>
       <c r="B40" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>137017885</v>
       </c>
       <c r="B41" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>136990648</v>
       </c>
       <c r="B43" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>136990653</v>
       </c>
       <c r="B44" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>136990657</v>
       </c>
       <c r="B45" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>136990664</v>
       </c>
       <c r="B46" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>136990665</v>
       </c>
       <c r="B47" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>136990667</v>
       </c>
       <c r="B48" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>136990679</v>
       </c>
       <c r="B49" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
         <v>136990680</v>
       </c>
       <c r="B50" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>136990686</v>
       </c>
       <c r="B51" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>136990688</v>
       </c>
       <c r="B52" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>136990690</v>
       </c>
       <c r="B53" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>136990692</v>
       </c>
       <c r="B54" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>137016888</v>
       </c>
       <c r="B55" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         <v>137017881</v>
       </c>
       <c r="B56" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>136990659</v>
       </c>
       <c r="B66" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>136990670</v>
       </c>
       <c r="B69" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>136990660</v>
       </c>
       <c r="B73" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>137017878</v>
       </c>
       <c r="B74" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>136990668</v>
       </c>
       <c r="B75" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>137016886</v>
       </c>
       <c r="B3" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>137016887</v>
       </c>
       <c r="B4" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136990661</v>
       </c>
       <c r="B11" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>136990666</v>
       </c>
       <c r="B12" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136990671</v>
       </c>
       <c r="B13" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>136990685</v>
       </c>
       <c r="B14" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>137017880</v>
       </c>
       <c r="B15" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>137017886</v>
       </c>
       <c r="B16" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>136990687</v>
       </c>
       <c r="B20" t="n">
-        <v>92169</v>
+        <v>92170</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>136990689</v>
       </c>
       <c r="B21" t="n">
-        <v>92169</v>
+        <v>92170</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>136990656</v>
       </c>
       <c r="B22" t="n">
-        <v>96619</v>
+        <v>96620</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>136990694</v>
       </c>
       <c r="B23" t="n">
-        <v>96619</v>
+        <v>96620</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136990655</v>
       </c>
       <c r="B24" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>136990691</v>
       </c>
       <c r="B25" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>136990652</v>
       </c>
       <c r="B33" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>136990658</v>
       </c>
       <c r="B34" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>136990669</v>
       </c>
       <c r="B35" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>136990683</v>
       </c>
       <c r="B36" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>136990684</v>
       </c>
       <c r="B37" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>137016885</v>
       </c>
       <c r="B38" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>137016889</v>
       </c>
       <c r="B39" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>137017883</v>
       </c>
       <c r="B40" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>137017885</v>
       </c>
       <c r="B41" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>137017878</v>
       </c>
       <c r="B74" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>136990668</v>
       </c>
       <c r="B75" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>137016886</v>
       </c>
       <c r="B3" t="n">
-        <v>92109</v>
+        <v>92112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>137016887</v>
       </c>
       <c r="B4" t="n">
-        <v>92109</v>
+        <v>92112</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136990661</v>
       </c>
       <c r="B11" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>136990666</v>
       </c>
       <c r="B12" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136990671</v>
       </c>
       <c r="B13" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>136990685</v>
       </c>
       <c r="B14" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>137017880</v>
       </c>
       <c r="B15" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>137017886</v>
       </c>
       <c r="B16" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>136990687</v>
       </c>
       <c r="B20" t="n">
-        <v>92170</v>
+        <v>92173</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>136990689</v>
       </c>
       <c r="B21" t="n">
-        <v>92170</v>
+        <v>92173</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>136990656</v>
       </c>
       <c r="B22" t="n">
-        <v>96620</v>
+        <v>96625</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>136990694</v>
       </c>
       <c r="B23" t="n">
-        <v>96620</v>
+        <v>96625</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136990655</v>
       </c>
       <c r="B24" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>136990691</v>
       </c>
       <c r="B25" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>136990652</v>
       </c>
       <c r="B33" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>136990658</v>
       </c>
       <c r="B34" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>136990669</v>
       </c>
       <c r="B35" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>136990683</v>
       </c>
       <c r="B36" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>136990684</v>
       </c>
       <c r="B37" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>137016885</v>
       </c>
       <c r="B38" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>137016889</v>
       </c>
       <c r="B39" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>137017883</v>
       </c>
       <c r="B40" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>137017885</v>
       </c>
       <c r="B41" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>136990648</v>
       </c>
       <c r="B43" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>136990653</v>
       </c>
       <c r="B44" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>136990657</v>
       </c>
       <c r="B45" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>136990664</v>
       </c>
       <c r="B46" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>136990665</v>
       </c>
       <c r="B47" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>136990667</v>
       </c>
       <c r="B48" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>136990679</v>
       </c>
       <c r="B49" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
         <v>136990680</v>
       </c>
       <c r="B50" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>136990686</v>
       </c>
       <c r="B51" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>136990688</v>
       </c>
       <c r="B52" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>136990690</v>
       </c>
       <c r="B53" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>136990692</v>
       </c>
       <c r="B54" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>137016888</v>
       </c>
       <c r="B55" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         <v>137017881</v>
       </c>
       <c r="B56" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>136990659</v>
       </c>
       <c r="B66" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>136990670</v>
       </c>
       <c r="B69" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>136990660</v>
       </c>
       <c r="B73" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>137017878</v>
       </c>
       <c r="B74" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>136990668</v>
       </c>
       <c r="B75" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>137016886</v>
       </c>
       <c r="B3" t="n">
-        <v>92112</v>
+        <v>92114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>137016887</v>
       </c>
       <c r="B4" t="n">
-        <v>92112</v>
+        <v>92114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136990661</v>
       </c>
       <c r="B11" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>136990666</v>
       </c>
       <c r="B12" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136990671</v>
       </c>
       <c r="B13" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>136990685</v>
       </c>
       <c r="B14" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>137017880</v>
       </c>
       <c r="B15" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>137017886</v>
       </c>
       <c r="B16" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>136990687</v>
       </c>
       <c r="B20" t="n">
-        <v>92173</v>
+        <v>92175</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>136990689</v>
       </c>
       <c r="B21" t="n">
-        <v>92173</v>
+        <v>92175</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>136990656</v>
       </c>
       <c r="B22" t="n">
-        <v>96625</v>
+        <v>96627</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>136990694</v>
       </c>
       <c r="B23" t="n">
-        <v>96625</v>
+        <v>96627</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136990655</v>
       </c>
       <c r="B24" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>136990691</v>
       </c>
       <c r="B25" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>136990652</v>
       </c>
       <c r="B33" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>136990658</v>
       </c>
       <c r="B34" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>136990669</v>
       </c>
       <c r="B35" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>136990683</v>
       </c>
       <c r="B36" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>136990684</v>
       </c>
       <c r="B37" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>137016885</v>
       </c>
       <c r="B38" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>137016889</v>
       </c>
       <c r="B39" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>137017883</v>
       </c>
       <c r="B40" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>137017885</v>
       </c>
       <c r="B41" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>137017878</v>
       </c>
       <c r="B74" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>136990668</v>
       </c>
       <c r="B75" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>137016886</v>
       </c>
       <c r="B3" t="n">
-        <v>92114</v>
+        <v>92119</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>137016887</v>
       </c>
       <c r="B4" t="n">
-        <v>92114</v>
+        <v>92119</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136990661</v>
       </c>
       <c r="B11" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>136990666</v>
       </c>
       <c r="B12" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136990671</v>
       </c>
       <c r="B13" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>136990685</v>
       </c>
       <c r="B14" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>137017880</v>
       </c>
       <c r="B15" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>137017886</v>
       </c>
       <c r="B16" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>136990687</v>
       </c>
       <c r="B20" t="n">
-        <v>92175</v>
+        <v>92180</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>136990689</v>
       </c>
       <c r="B21" t="n">
-        <v>92175</v>
+        <v>92180</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>136990656</v>
       </c>
       <c r="B22" t="n">
-        <v>96627</v>
+        <v>96633</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>136990694</v>
       </c>
       <c r="B23" t="n">
-        <v>96627</v>
+        <v>96633</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136990655</v>
       </c>
       <c r="B24" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>136990691</v>
       </c>
       <c r="B25" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>136990652</v>
       </c>
       <c r="B33" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>136990658</v>
       </c>
       <c r="B34" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>136990669</v>
       </c>
       <c r="B35" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>136990683</v>
       </c>
       <c r="B36" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>136990684</v>
       </c>
       <c r="B37" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>137016885</v>
       </c>
       <c r="B38" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>137016889</v>
       </c>
       <c r="B39" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>137017883</v>
       </c>
       <c r="B40" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>137017885</v>
       </c>
       <c r="B41" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>136990648</v>
       </c>
       <c r="B43" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>136990653</v>
       </c>
       <c r="B44" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>136990657</v>
       </c>
       <c r="B45" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>136990664</v>
       </c>
       <c r="B46" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>136990665</v>
       </c>
       <c r="B47" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>136990667</v>
       </c>
       <c r="B48" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>136990679</v>
       </c>
       <c r="B49" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
         <v>136990680</v>
       </c>
       <c r="B50" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>136990686</v>
       </c>
       <c r="B51" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>136990688</v>
       </c>
       <c r="B52" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>136990690</v>
       </c>
       <c r="B53" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>136990692</v>
       </c>
       <c r="B54" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>137016888</v>
       </c>
       <c r="B55" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         <v>137017881</v>
       </c>
       <c r="B56" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>136990659</v>
       </c>
       <c r="B66" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>136990670</v>
       </c>
       <c r="B69" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>136990660</v>
       </c>
       <c r="B73" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>137017878</v>
       </c>
       <c r="B74" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>136990668</v>
       </c>
       <c r="B75" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -9114,7 +9114,7 @@
         <v>137017878</v>
       </c>
       <c r="B74" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>137016886</v>
       </c>
       <c r="B3" t="n">
-        <v>92119</v>
+        <v>92131</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>137016887</v>
       </c>
       <c r="B4" t="n">
-        <v>92119</v>
+        <v>92131</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136990661</v>
       </c>
       <c r="B11" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>136990666</v>
       </c>
       <c r="B12" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136990671</v>
       </c>
       <c r="B13" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>136990685</v>
       </c>
       <c r="B14" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>137017880</v>
       </c>
       <c r="B15" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>137017886</v>
       </c>
       <c r="B16" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>136990687</v>
       </c>
       <c r="B20" t="n">
-        <v>92180</v>
+        <v>92192</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>136990689</v>
       </c>
       <c r="B21" t="n">
-        <v>92180</v>
+        <v>92192</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>136990656</v>
       </c>
       <c r="B22" t="n">
-        <v>96633</v>
+        <v>96645</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>136990694</v>
       </c>
       <c r="B23" t="n">
-        <v>96633</v>
+        <v>96645</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136990655</v>
       </c>
       <c r="B24" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>136990691</v>
       </c>
       <c r="B25" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>136990652</v>
       </c>
       <c r="B33" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>136990658</v>
       </c>
       <c r="B34" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>136990669</v>
       </c>
       <c r="B35" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>136990683</v>
       </c>
       <c r="B36" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>136990684</v>
       </c>
       <c r="B37" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>137016885</v>
       </c>
       <c r="B38" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>137016889</v>
       </c>
       <c r="B39" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>137017883</v>
       </c>
       <c r="B40" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>137017885</v>
       </c>
       <c r="B41" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>136990648</v>
       </c>
       <c r="B43" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>136990653</v>
       </c>
       <c r="B44" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>136990657</v>
       </c>
       <c r="B45" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>136990664</v>
       </c>
       <c r="B46" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>136990665</v>
       </c>
       <c r="B47" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>136990667</v>
       </c>
       <c r="B48" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>136990679</v>
       </c>
       <c r="B49" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
         <v>136990680</v>
       </c>
       <c r="B50" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>136990686</v>
       </c>
       <c r="B51" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>136990688</v>
       </c>
       <c r="B52" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>136990690</v>
       </c>
       <c r="B53" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>136990692</v>
       </c>
       <c r="B54" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>137016888</v>
       </c>
       <c r="B55" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         <v>137017881</v>
       </c>
       <c r="B56" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>137017878</v>
       </c>
       <c r="B74" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>136990668</v>
       </c>
       <c r="B75" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>137016886</v>
       </c>
       <c r="B3" t="n">
-        <v>92131</v>
+        <v>92132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>137016887</v>
       </c>
       <c r="B4" t="n">
-        <v>92131</v>
+        <v>92132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136990661</v>
       </c>
       <c r="B11" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>136990666</v>
       </c>
       <c r="B12" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136990671</v>
       </c>
       <c r="B13" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>136990685</v>
       </c>
       <c r="B14" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>137017880</v>
       </c>
       <c r="B15" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>137017886</v>
       </c>
       <c r="B16" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>136990687</v>
       </c>
       <c r="B20" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>136990689</v>
       </c>
       <c r="B21" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>136990656</v>
       </c>
       <c r="B22" t="n">
-        <v>96645</v>
+        <v>96646</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>136990694</v>
       </c>
       <c r="B23" t="n">
-        <v>96645</v>
+        <v>96646</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136990655</v>
       </c>
       <c r="B24" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>136990691</v>
       </c>
       <c r="B25" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>136990652</v>
       </c>
       <c r="B33" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>136990658</v>
       </c>
       <c r="B34" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>136990669</v>
       </c>
       <c r="B35" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>136990683</v>
       </c>
       <c r="B36" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>136990684</v>
       </c>
       <c r="B37" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>137016885</v>
       </c>
       <c r="B38" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>137016889</v>
       </c>
       <c r="B39" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>137017883</v>
       </c>
       <c r="B40" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>137017885</v>
       </c>
       <c r="B41" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>136990648</v>
       </c>
       <c r="B43" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>136990653</v>
       </c>
       <c r="B44" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>136990657</v>
       </c>
       <c r="B45" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>136990664</v>
       </c>
       <c r="B46" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>136990665</v>
       </c>
       <c r="B47" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>136990667</v>
       </c>
       <c r="B48" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>136990679</v>
       </c>
       <c r="B49" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
         <v>136990680</v>
       </c>
       <c r="B50" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>136990686</v>
       </c>
       <c r="B51" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>136990688</v>
       </c>
       <c r="B52" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>136990690</v>
       </c>
       <c r="B53" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>136990692</v>
       </c>
       <c r="B54" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>137016888</v>
       </c>
       <c r="B55" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         <v>137017881</v>
       </c>
       <c r="B56" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>137017878</v>
       </c>
       <c r="B74" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>136990668</v>
       </c>
       <c r="B75" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>137016886</v>
       </c>
       <c r="B3" t="n">
-        <v>92132</v>
+        <v>92135</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>137016887</v>
       </c>
       <c r="B4" t="n">
-        <v>92132</v>
+        <v>92135</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136990661</v>
       </c>
       <c r="B11" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>136990666</v>
       </c>
       <c r="B12" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136990671</v>
       </c>
       <c r="B13" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>136990685</v>
       </c>
       <c r="B14" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>137017880</v>
       </c>
       <c r="B15" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>137017886</v>
       </c>
       <c r="B16" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>136990687</v>
       </c>
       <c r="B20" t="n">
-        <v>92193</v>
+        <v>92196</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>136990689</v>
       </c>
       <c r="B21" t="n">
-        <v>92193</v>
+        <v>92196</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>136990656</v>
       </c>
       <c r="B22" t="n">
-        <v>96646</v>
+        <v>96649</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>136990694</v>
       </c>
       <c r="B23" t="n">
-        <v>96646</v>
+        <v>96649</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136990655</v>
       </c>
       <c r="B24" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>136990691</v>
       </c>
       <c r="B25" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>136990652</v>
       </c>
       <c r="B33" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>136990658</v>
       </c>
       <c r="B34" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>136990669</v>
       </c>
       <c r="B35" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>136990683</v>
       </c>
       <c r="B36" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>136990684</v>
       </c>
       <c r="B37" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>137016885</v>
       </c>
       <c r="B38" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>137016889</v>
       </c>
       <c r="B39" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>137017883</v>
       </c>
       <c r="B40" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>137017885</v>
       </c>
       <c r="B41" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>136990648</v>
       </c>
       <c r="B43" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>136990653</v>
       </c>
       <c r="B44" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>136990657</v>
       </c>
       <c r="B45" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>136990664</v>
       </c>
       <c r="B46" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>136990665</v>
       </c>
       <c r="B47" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>136990667</v>
       </c>
       <c r="B48" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>136990679</v>
       </c>
       <c r="B49" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
         <v>136990680</v>
       </c>
       <c r="B50" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>136990686</v>
       </c>
       <c r="B51" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>136990688</v>
       </c>
       <c r="B52" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>136990690</v>
       </c>
       <c r="B53" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>136990692</v>
       </c>
       <c r="B54" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>137016888</v>
       </c>
       <c r="B55" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         <v>137017881</v>
       </c>
       <c r="B56" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>137017878</v>
       </c>
       <c r="B74" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>136990668</v>
       </c>
       <c r="B75" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>137016886</v>
       </c>
       <c r="B3" t="n">
-        <v>92135</v>
+        <v>92136</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>137016887</v>
       </c>
       <c r="B4" t="n">
-        <v>92135</v>
+        <v>92136</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136990661</v>
       </c>
       <c r="B11" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>136990666</v>
       </c>
       <c r="B12" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136990671</v>
       </c>
       <c r="B13" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>136990685</v>
       </c>
       <c r="B14" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>137017880</v>
       </c>
       <c r="B15" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>137017886</v>
       </c>
       <c r="B16" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>136990687</v>
       </c>
       <c r="B20" t="n">
-        <v>92196</v>
+        <v>92197</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>136990689</v>
       </c>
       <c r="B21" t="n">
-        <v>92196</v>
+        <v>92197</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>136990656</v>
       </c>
       <c r="B22" t="n">
-        <v>96649</v>
+        <v>96650</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>136990694</v>
       </c>
       <c r="B23" t="n">
-        <v>96649</v>
+        <v>96650</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136990655</v>
       </c>
       <c r="B24" t="n">
-        <v>96646</v>
+        <v>96647</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>136990691</v>
       </c>
       <c r="B25" t="n">
-        <v>96646</v>
+        <v>96647</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>136990652</v>
       </c>
       <c r="B33" t="n">
-        <v>92148</v>
+        <v>92149</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>136990658</v>
       </c>
       <c r="B34" t="n">
-        <v>92148</v>
+        <v>92149</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>136990669</v>
       </c>
       <c r="B35" t="n">
-        <v>92148</v>
+        <v>92149</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>136990683</v>
       </c>
       <c r="B36" t="n">
-        <v>92148</v>
+        <v>92149</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>136990684</v>
       </c>
       <c r="B37" t="n">
-        <v>92148</v>
+        <v>92149</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>137016885</v>
       </c>
       <c r="B38" t="n">
-        <v>92148</v>
+        <v>92149</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>137016889</v>
       </c>
       <c r="B39" t="n">
-        <v>92148</v>
+        <v>92149</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>137017883</v>
       </c>
       <c r="B40" t="n">
-        <v>92148</v>
+        <v>92149</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>137017885</v>
       </c>
       <c r="B41" t="n">
-        <v>92148</v>
+        <v>92149</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>136990648</v>
       </c>
       <c r="B43" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>136990653</v>
       </c>
       <c r="B44" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>136990657</v>
       </c>
       <c r="B45" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>136990664</v>
       </c>
       <c r="B46" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>136990665</v>
       </c>
       <c r="B47" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>136990667</v>
       </c>
       <c r="B48" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>136990679</v>
       </c>
       <c r="B49" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
         <v>136990680</v>
       </c>
       <c r="B50" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>136990686</v>
       </c>
       <c r="B51" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>136990688</v>
       </c>
       <c r="B52" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>136990690</v>
       </c>
       <c r="B53" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>136990692</v>
       </c>
       <c r="B54" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>137016888</v>
       </c>
       <c r="B55" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         <v>137017881</v>
       </c>
       <c r="B56" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>137017878</v>
       </c>
       <c r="B74" t="n">
-        <v>111430</v>
+        <v>111432</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>136990668</v>
       </c>
       <c r="B75" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>137016886</v>
       </c>
       <c r="B3" t="n">
-        <v>92136</v>
+        <v>92139</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>137016887</v>
       </c>
       <c r="B4" t="n">
-        <v>92136</v>
+        <v>92139</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136990661</v>
       </c>
       <c r="B11" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>136990666</v>
       </c>
       <c r="B12" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136990671</v>
       </c>
       <c r="B13" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>136990685</v>
       </c>
       <c r="B14" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>137017880</v>
       </c>
       <c r="B15" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>137017886</v>
       </c>
       <c r="B16" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>136990687</v>
       </c>
       <c r="B20" t="n">
-        <v>92197</v>
+        <v>92200</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>136990689</v>
       </c>
       <c r="B21" t="n">
-        <v>92197</v>
+        <v>92200</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>136990656</v>
       </c>
       <c r="B22" t="n">
-        <v>96650</v>
+        <v>96653</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>136990694</v>
       </c>
       <c r="B23" t="n">
-        <v>96650</v>
+        <v>96653</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136990655</v>
       </c>
       <c r="B24" t="n">
-        <v>96647</v>
+        <v>96650</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>136990691</v>
       </c>
       <c r="B25" t="n">
-        <v>96647</v>
+        <v>96650</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>136990652</v>
       </c>
       <c r="B33" t="n">
-        <v>92149</v>
+        <v>92152</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>136990658</v>
       </c>
       <c r="B34" t="n">
-        <v>92149</v>
+        <v>92152</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>136990669</v>
       </c>
       <c r="B35" t="n">
-        <v>92149</v>
+        <v>92152</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>136990683</v>
       </c>
       <c r="B36" t="n">
-        <v>92149</v>
+        <v>92152</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>136990684</v>
       </c>
       <c r="B37" t="n">
-        <v>92149</v>
+        <v>92152</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>137016885</v>
       </c>
       <c r="B38" t="n">
-        <v>92149</v>
+        <v>92152</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>137016889</v>
       </c>
       <c r="B39" t="n">
-        <v>92149</v>
+        <v>92152</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>137017883</v>
       </c>
       <c r="B40" t="n">
-        <v>92149</v>
+        <v>92152</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>137017885</v>
       </c>
       <c r="B41" t="n">
-        <v>92149</v>
+        <v>92152</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>136990648</v>
       </c>
       <c r="B43" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>136990653</v>
       </c>
       <c r="B44" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>136990657</v>
       </c>
       <c r="B45" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>136990664</v>
       </c>
       <c r="B46" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>136990665</v>
       </c>
       <c r="B47" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>136990667</v>
       </c>
       <c r="B48" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>136990679</v>
       </c>
       <c r="B49" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
         <v>136990680</v>
       </c>
       <c r="B50" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>136990686</v>
       </c>
       <c r="B51" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>136990688</v>
       </c>
       <c r="B52" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>136990690</v>
       </c>
       <c r="B53" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>136990692</v>
       </c>
       <c r="B54" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>137016888</v>
       </c>
       <c r="B55" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         <v>137017881</v>
       </c>
       <c r="B56" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>136990659</v>
       </c>
       <c r="B66" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>136990670</v>
       </c>
       <c r="B69" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>136990660</v>
       </c>
       <c r="B73" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>137017878</v>
       </c>
       <c r="B74" t="n">
-        <v>111432</v>
+        <v>111436</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>136990668</v>
       </c>
       <c r="B75" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
